--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/jul-2025.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/jul-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC jul-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC jul-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -614,7 +614,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2517,7 +2517,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">

--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/jul-2025.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/jul-2025.xlsx
@@ -627,7 +627,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -688,7 +692,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -749,7 +757,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -810,7 +822,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -871,7 +887,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -932,7 +952,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -993,7 +1017,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1054,7 +1082,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1115,7 +1147,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1237,7 +1273,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1298,7 +1338,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1359,7 +1403,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1420,7 +1468,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1481,7 +1533,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1607,7 +1663,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1668,7 +1728,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1729,7 +1793,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1790,7 +1858,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1851,7 +1923,11 @@
           <t>96.545.450-0</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1912,7 +1988,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2038,7 +2118,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2099,7 +2183,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2225,7 +2313,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2286,7 +2378,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2408,7 +2504,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2469,7 +2569,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2530,7 +2634,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2591,7 +2699,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2652,7 +2764,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2713,7 +2829,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2904,7 +3024,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2965,7 +3089,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3026,7 +3154,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3087,7 +3219,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3148,7 +3284,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3209,7 +3349,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3270,7 +3414,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3331,7 +3479,11 @@
           <t>84.807.200-1</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3392,7 +3544,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3453,7 +3609,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3514,7 +3674,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3575,7 +3739,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3701,7 +3869,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3884,7 +4056,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4010,7 +4186,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4071,7 +4251,11 @@
           <t>96.918.300-5</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
